--- a/docs/таблицы карт/КАРТЫ — свод 1.50.0.xlsx
+++ b/docs/таблицы карт/КАРТЫ — свод 1.50.0.xlsx
@@ -1150,7 +1150,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНАЯ ДОБЫЧА</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1160,14 +1160,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">free_action</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{action=mining}</t>
-        </is>
-      </c>
+          <t xml:space="preserve">energy_or_modules</t>
+        </is>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2">
         <v>4</v>
       </c>
@@ -1183,27 +1179,31 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_01, z3_04, z3_07, z3_10</t>
+          <t xml:space="preserve">z3_09, z3_12, z3_15, z3_18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">действие (СПЕЦ)</t>
+          <t xml:space="preserve">свободное (∞)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">energy_or_modules</t>
-        </is>
-      </c>
-      <c r="D5" s="2"/>
+          <t xml:space="preserve">module_swap</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{free=true}</t>
+        </is>
+      </c>
       <c r="E5" s="2">
         <v>4</v>
       </c>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_11, z3_14, z3_17, z3_20</t>
+          <t xml:space="preserve">z3_10, z3_13, z3_16, z3_50</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_40, z3_43, z3_46, z3_49</t>
+          <t xml:space="preserve">z3_38, z3_41, z3_44, z3_47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ</t>
+          <t xml:space="preserve">СВОБОДНАЯ ДОБЫЧА</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=build, ops=1}</t>
+          <t xml:space="preserve">{action=mining}</t>
         </is>
       </c>
       <c r="E7" s="2">
@@ -1299,29 +1299,29 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_02, z3_05, z3_08</t>
+          <t xml:space="preserve">z3_01, z3_04, z3_07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">КОНВЕРСИЯ: 1 келемий -&gt; 1 трофей</t>
+          <t xml:space="preserve">ОДНА СТРОИТЕЛЬНАЯ ОПЕРАЦИЯ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ресурс (СПЕЦ)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">convert</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{amount=1, from=kelium, to=trophy}</t>
+          <t xml:space="preserve">{action=build, ops=1}</t>
         </is>
       </c>
       <c r="E8" s="2">
@@ -1339,29 +1339,29 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_03, z3_06, z3_09</t>
+          <t xml:space="preserve">z3_02, z3_05, z3_08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
+          <t xml:space="preserve">ЩИТ: техника или авиация</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">свободное (∞)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">module_swap</t>
+          <t xml:space="preserve">shield</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{free=true}</t>
+          <t xml:space="preserve">{kinds=[vehicle, aircraft]}</t>
         </is>
       </c>
       <c r="E9" s="2">
@@ -1379,14 +1379,14 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_12, z3_15, z3_18</t>
+          <t xml:space="preserve">z3_11, z3_14, z3_17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: техника или авиация</t>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shield</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kinds=[vehicle, aircraft]}</t>
+          <t xml:space="preserve">{action=movement}</t>
         </is>
       </c>
       <c r="E10" s="2">
@@ -1419,14 +1419,14 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_13, z3_16, z3_19</t>
+          <t xml:space="preserve">z3_28, z3_32, z3_36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=movement}</t>
+          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
         </is>
       </c>
       <c r="E11" s="2">
@@ -1459,29 +1459,29 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_30, z3_34, z3_38</t>
+          <t xml:space="preserve">z3_29, z3_33, z3_37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">действие (СПЕЦ)</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">free_action</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=combat, attack_tokens=1}</t>
+          <t xml:space="preserve">{kind=withdraw}</t>
         </is>
       </c>
       <c r="E12" s="2">
@@ -1499,31 +1499,27 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_31, z3_35, z3_39</t>
+          <t xml:space="preserve">z3_30, z3_34, z3_48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
+          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">в моменте (реакция)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reaction</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{kind=withdraw}</t>
-        </is>
-      </c>
+          <t xml:space="preserve">speed_boost</t>
+        </is>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2">
         <v>3</v>
       </c>
@@ -1539,7 +1535,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_32, z3_36, z3_50</t>
+          <t xml:space="preserve">z3_31, z3_35, z3_49</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1575,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_41, z3_44, z3_47</t>
+          <t xml:space="preserve">z3_39, z3_42, z3_45</t>
         </is>
       </c>
     </row>
@@ -1619,29 +1615,29 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_42, z3_45, z3_48</t>
+          <t xml:space="preserve">z3_40, z3_43, z3_46</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ</t>
+          <t xml:space="preserve">КОНВЕРСИЯ: 1 келемий -&gt; 1 трофей</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">действие (СПЕЦ)</t>
+          <t xml:space="preserve">ресурс (СПЕЦ)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">free_action</t>
+          <t xml:space="preserve">convert</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{action=assembly, buildings=1}</t>
+          <t xml:space="preserve">{amount=1, from=kelium, to=trophy}</t>
         </is>
       </c>
       <c r="E16" s="2">
@@ -1659,14 +1655,14 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_21, z3_25</t>
+          <t xml:space="preserve">z3_03, z3_06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+          <t xml:space="preserve">СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1676,12 +1672,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">deploy_units</t>
+          <t xml:space="preserve">free_action</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{count=1}</t>
+          <t xml:space="preserve">{action=assembly, buildings=1}</t>
         </is>
       </c>
       <c r="E17" s="2">
@@ -1699,29 +1695,29 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_22, z3_26</t>
+          <t xml:space="preserve">z3_19, z3_23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЗАКРОМА. Получи 2 боеприпаса, если кто-либо атакует твой жетон</t>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">в моменте (реакция)</t>
+          <t xml:space="preserve">действие (СПЕЦ)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reaction</t>
+          <t xml:space="preserve">deploy_units</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kind=ammo_on_attack}</t>
+          <t xml:space="preserve">{count=1}</t>
         </is>
       </c>
       <c r="E18" s="2">
@@ -1739,29 +1735,29 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_23, z3_27</t>
+          <t xml:space="preserve">z3_20, z3_24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: пехота или авиация</t>
+          <t xml:space="preserve">ЗАКРОМА. Получи 2 боеприпаса, если кто-либо атакует твой жетон</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">действие (СПЕЦ)</t>
+          <t xml:space="preserve">в моменте (реакция)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shield</t>
+          <t xml:space="preserve">reaction</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{kinds=[infantry, aircraft]}</t>
+          <t xml:space="preserve">{kind=ammo_on_attack}</t>
         </is>
       </c>
       <c r="E19" s="2">
@@ -1779,14 +1775,14 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_24, z3_28</t>
+          <t xml:space="preserve">z3_21, z3_25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
+          <t xml:space="preserve">ЩИТ: пехота или авиация</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1796,10 +1792,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">speed_boost</t>
-        </is>
-      </c>
-      <c r="D20" s="2"/>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{kinds=[infantry, aircraft]}</t>
+        </is>
+      </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_33, z3_37</t>
+          <t xml:space="preserve">z3_22, z3_26</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">z3_29</t>
+          <t xml:space="preserve">z3_27</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лестница добытчиков ×3</t>
+          <t xml:space="preserve">Запитанный добытчик ×2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои добытчики 3 разных уровней</t>
+          <t xml:space="preserve">Имей на поле 2 своих запитанных добытчика</t>
         </is>
       </c>
       <c r="F6" s="2"/>
@@ -3393,21 +3393,27 @@
           <t xml:space="preserve">build_miner|energy_swap</t>
         </is>
       </c>
-      <c r="K6" s="2">
-        <v>2</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2">
         <v>0.0</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей на поле 3 своих запитанных добытчика</t>
+        </is>
+      </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
+      <c r="Q6" s="2">
+        <v>1</v>
+      </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="S6" s="2">
+        <v>3</v>
+      </c>
       <c r="T6" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
@@ -3416,7 +3422,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои добытчики 3 разных уровней — награда на выбор: Построить добытчик или Питание и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле 2 своих запитанных добытчика — награда на выбор: Построить добытчик или Питание. Дополнительно — имей на поле 3 своих запитанных добытчика: 1 карта арсенала и три спец-действия.</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3434,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Добытчик 3-го уровня ×1</t>
+          <t xml:space="preserve">Добытчик рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3443,7 +3449,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свой добытчик 3-го уровня или выше</t>
+          <t xml:space="preserve">Имей свой добытчик на гексе, соседнем с гексом, где есть здание врага</t>
         </is>
       </c>
       <c r="F7" s="2"/>
@@ -3461,7 +3467,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей на поле 2 своих добытчика 3-го уровня или выше</t>
+          <t xml:space="preserve">имей свои добытчики на 2 разных гексах, соседних с гексами, где есть здание врага</t>
         </is>
       </c>
       <c r="N7" s="2"/>
@@ -3484,7 +3490,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свой добытчик 3-го уровня или выше — награда на выбор: Добыча или Построить энергостанцию. Дополнительно — имей на поле 2 своих добытчика 3-го уровня или выше: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей свой добытчик на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Добыча или Построить энергостанцию. Дополнительно — имей свои добытчики на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3502,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уровни хозяйства 10+</t>
+          <t xml:space="preserve">Добытчик рядом с врагом ×2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3511,7 +3517,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои добытчики и энергостанции с суммой уровней 10 или больше</t>
+          <t xml:space="preserve">Имей свои добытчики на 2 разных гексах, соседних с гексами, где есть здание врага</t>
         </is>
       </c>
       <c r="F8" s="2"/>
@@ -3523,21 +3529,27 @@
           <t xml:space="preserve">build_miner|build_plant</t>
         </is>
       </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2">
         <v>0.0</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей свои добытчики на 3 разных гексах, соседних с гексами, где есть здание врага</t>
+        </is>
+      </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
+      <c r="Q8" s="2">
+        <v>1</v>
+      </c>
       <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+      <c r="S8" s="2">
+        <v>3</v>
+      </c>
       <c r="T8" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
@@ -3546,7 +3558,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои добытчики и энергостанции с суммой уровней 10 или больше — награда на выбор: Построить добытчик или Построить энергостанцию и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей свои добытчики на 2 разных гексах, соседних с гексами, где есть здание врага — награда на выбор: Построить добытчик или Построить энергостанцию. Дополнительно — имей свои добытчики на 3 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и три спец-действия.</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3570,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запитанный добытчик ×2</t>
+          <t xml:space="preserve">Потрать келемий ×2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3568,12 +3580,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих запитанных добытчика</t>
+          <t xml:space="preserve">В ЭТОТ ХОД потрать 2 келемия</t>
         </is>
       </c>
       <c r="F9" s="2"/>
@@ -3585,27 +3597,21 @@
           <t xml:space="preserve">mining|energy_swap</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2">
+        <v>3</v>
+      </c>
       <c r="L9" s="2">
         <v>0.0</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей на поле 3 своих запитанных добытчика</t>
-        </is>
-      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
-      <c r="Q9" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="2">
-        <v>3</v>
-      </c>
+      <c r="S9" s="2"/>
       <c r="T9" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
@@ -3614,7 +3620,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих запитанных добытчика — награда на выбор: Добыча или Питание. Дополнительно — имей на поле 3 своих запитанных добытчика: 1 карта арсенала и три спец-действия.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД потрать 2 келемия — награда на выбор: Добыча или Питание и три спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3632,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Добытчик рядом с врагом ×1</t>
+          <t xml:space="preserve">Энергостанция ×3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3641,7 +3647,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой добытчик на гексе, соседнем с гексом, где есть здание врага</t>
+          <t xml:space="preserve">Имей на поле 3 своих энергостанции</t>
         </is>
       </c>
       <c r="F10" s="2"/>
@@ -3650,7 +3656,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_miner|energy_swap</t>
+          <t xml:space="preserve">build_plant|assembly</t>
         </is>
       </c>
       <c r="K10" s="2"/>
@@ -3659,7 +3665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей свои добытчики на 2 разных гексах, соседних с гексами, где есть здание врага</t>
+          <t xml:space="preserve">имей на поле 4 своих энергостанции</t>
         </is>
       </c>
       <c r="N10" s="2"/>
@@ -3677,12 +3683,12 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">КОНВЕРСИЯ: 1 келемий -&gt; 1 трофей</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой добытчик на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Построить добытчик или Питание. Дополнительно — имей свои добытчики на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей на поле 3 своих энергостанции — награда на выбор: Построить энергостанцию или Снабжение. Дополнительно — имей на поле 4 своих энергостанции: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3700,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лестница добытчиков ×2</t>
+          <t xml:space="preserve">Энергостанция рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3709,7 +3715,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои добытчики 2 разных уровней</t>
+          <t xml:space="preserve">Имей свою энергостанцию на гексе, соседнем с гексом, где есть добытчик врага</t>
         </is>
       </c>
       <c r="F11" s="2"/>
@@ -3718,33 +3724,39 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mining|build_plant</t>
-        </is>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">energy_swap|build_military</t>
+        </is>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2">
         <v>0.0</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей свои энергостанции на 2 разных гексах, соседних с гексами, где есть добытчик врага</t>
+        </is>
+      </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="Q11" s="2">
+        <v>1</v>
+      </c>
       <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+      <c r="S11" s="2">
+        <v>2</v>
+      </c>
       <c r="T11" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНАЯ ДОБЫЧА</t>
+          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои добытчики 2 разных уровней — награда на выбор: Добыча или Построить энергостанцию и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей свою энергостанцию на гексе, соседнем с гексом, где есть добытчик врага — награда на выбор: Питание или Построить военное здание. Дополнительно — имей свои энергостанции на 2 разных гексах, соседних с гексами, где есть добытчик врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3768,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энергостанция ×3</t>
+          <t xml:space="preserve">Запитай ×2</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3766,15 +3778,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 3 своих энергостанции</t>
-        </is>
-      </c>
-      <c r="F12" s="2"/>
+          <t xml:space="preserve">В ЭТОТ ХОД запитай 2 своих здания</t>
+        </is>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -3783,36 +3797,30 @@
           <t xml:space="preserve">build_plant|build_military</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
+      <c r="K12" s="2">
+        <v>2</v>
+      </c>
       <c r="L12" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей на поле 4 своих энергостанции</t>
-        </is>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
-      <c r="Q12" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="2">
-        <v>2</v>
-      </c>
+      <c r="S12" s="2"/>
       <c r="T12" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t xml:space="preserve">ЩИТ: техника или авиация</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 3 своих энергостанции — награда на выбор: Построить энергостанцию или Построить военное здание. Дополнительно — имей на поле 4 своих энергостанции: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД запитай 2 своих здания — награда на выбор: Построить энергостанцию или Построить военное здание и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3832,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энергостанция рядом с врагом ×1</t>
+          <t xml:space="preserve">Уровни хозяйства 10+</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3839,7 +3847,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свою энергостанцию на гексе, соседнем с гексом, где есть добытчик врага</t>
+          <t xml:space="preserve">Имей на поле свои добытчики и энергостанции с суммой уровней 10 или больше</t>
         </is>
       </c>
       <c r="F13" s="2"/>
@@ -3851,36 +3859,30 @@
           <t xml:space="preserve">energy_swap|assembly</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
       <c r="L13" s="2">
         <v>0.0</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей свои энергостанции на 2 разных гексах, соседних с гексами, где есть добытчик врага</t>
-        </is>
-      </c>
+      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
-      <c r="Q13" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="2">
-        <v>2</v>
-      </c>
+      <c r="S13" s="2"/>
       <c r="T13" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свою энергостанцию на гексе, соседнем с гексом, где есть добытчик врага — награда на выбор: Питание или Снабжение. Дополнительно — имей свои энергостанции на 2 разных гексах, соседних с гексами, где есть добытчик врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей на поле свои добытчики и энергостанции с суммой уровней 10 или больше — награда на выбор: Питание или Снабжение и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3894,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запитай ×2</t>
+          <t xml:space="preserve">Лестница станций ×3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3902,17 +3904,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД запитай 2 своих здания</t>
-        </is>
-      </c>
-      <c r="F14" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей на поле свои энергостанции 3 разных уровней</t>
+        </is>
+      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="L14" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -3935,16 +3935,16 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: техника или авиация</t>
+          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД запитай 2 своих здания — награда на выбор: Построить энергостанцию или Снабжение и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле свои энергостанции 3 разных уровней — награда на выбор: Построить энергостанцию или Снабжение и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уровни станций 8+</t>
+          <t xml:space="preserve">Энергия в ячейках ×4</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои энергостанции с суммой уровней 8 или больше</t>
+          <t xml:space="preserve">Имей в ячейках своих зданий 4 кубика энергии</t>
         </is>
       </c>
       <c r="F15" s="2"/>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t xml:space="preserve">ЩИТ: техника или авиация</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои энергостанции с суммой уровней 8 или больше — награда на выбор: Питание или Построить военное здание и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей в ячейках своих зданий 4 кубика энергии — награда на выбор: Питание или Построить военное здание и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лестница станций ×3</t>
+          <t xml:space="preserve">Всё запитано</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4033,10 +4033,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои энергостанции 3 разных уровней</t>
-        </is>
-      </c>
-      <c r="F16" s="2"/>
+          <t xml:space="preserve">Имей на поле не меньше 2 своих добытчиков, и все они запитаны</t>
+        </is>
+      </c>
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -4049,7 +4051,7 @@
         <v>2</v>
       </c>
       <c r="L16" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -4059,16 +4061,16 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои энергостанции 3 разных уровней — награда на выбор: Построить энергостанцию или Построить военное здание и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле не меньше 2 своих добытчиков, и все они запитаны — награда на выбор: Построить энергостанцию или Построить военное здание и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4082,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Энергия в ячейках ×4</t>
+          <t xml:space="preserve">Крупная постройка</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4090,15 +4092,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей в ячейках своих зданий 4 кубика энергии</t>
-        </is>
-      </c>
-      <c r="F17" s="2"/>
+          <t xml:space="preserve">В ЭТОТ ХОД построй добытчик или энергостанцию 3-го уровня или выше</t>
+        </is>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -4111,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="L17" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -4121,16 +4125,16 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: техника или авиация</t>
+          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей в ячейках своих зданий 4 кубика энергии — награда на выбор: Питание или Снабжение и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД построй добытчик или энергостанцию 3-го уровня или выше — награда на выбор: Питание или Снабжение и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4146,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Всё запитано</t>
+          <t xml:space="preserve">Запитанная энергостанция ×3</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -4157,12 +4161,10 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле не меньше 2 своих добытчиков, и все они запитаны</t>
-        </is>
-      </c>
-      <c r="F18" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей на поле 3 своих запитанных энергостанции</t>
+        </is>
+      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -4171,30 +4173,36 @@
           <t xml:space="preserve">build_plant|assembly</t>
         </is>
       </c>
-      <c r="K18" s="2">
-        <v>2</v>
-      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M18" s="2"/>
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей на поле 4 своих запитанных энергостанции</t>
+        </is>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
+      <c r="Q18" s="2">
+        <v>1</v>
+      </c>
       <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+      <c r="S18" s="2">
+        <v>2</v>
+      </c>
       <c r="T18" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t xml:space="preserve">ЩИТ: техника или авиация</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле не меньше 2 своих добытчиков, и все они запитаны — награда на выбор: Построить энергостанцию или Снабжение и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле 3 своих запитанных энергостанции — награда на выбор: Построить энергостанцию или Снабжение. Дополнительно — имей на поле 4 своих запитанных энергостанции: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4214,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крупная постройка</t>
+          <t xml:space="preserve">Всё запитано</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4216,12 +4224,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД построй добытчик или энергостанцию 3-го уровня или выше</t>
+          <t xml:space="preserve">Имей на поле не меньше 2 своих зданий, и все они запитаны</t>
         </is>
       </c>
       <c r="F19" s="2">
@@ -4253,12 +4261,12 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
+          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД построй добытчик или энергостанцию 3-го уровня или выше — награда на выбор: Питание или Построить военное здание и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле не меньше 2 своих зданий, и все они запитаны — награда на выбор: Питание или Построить военное здание и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4278,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запитанная энергостанция ×3</t>
+          <t xml:space="preserve">Военное здание ×2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4285,7 +4293,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 3 своих запитанных энергостанции</t>
+          <t xml:space="preserve">Имей на поле 2 своих военных здания</t>
         </is>
       </c>
       <c r="F20" s="2"/>
@@ -4294,7 +4302,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_plant|build_military</t>
+          <t xml:space="preserve">build_military|combat</t>
         </is>
       </c>
       <c r="K20" s="2"/>
@@ -4303,7 +4311,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей на поле 4 своих запитанных энергостанции</t>
+          <t xml:space="preserve">имей на поле 3 своих военных здания</t>
         </is>
       </c>
       <c r="N20" s="2"/>
@@ -4321,12 +4329,12 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: техника или авиация</t>
+          <t xml:space="preserve">СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 3 своих запитанных энергостанции — награда на выбор: Построить энергостанцию или Построить военное здание. Дополнительно — имей на поле 4 своих запитанных энергостанции: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей на поле 2 своих военных здания — награда на выбор: Построить военное здание или Бой. Дополнительно — имей на поле 3 своих военных здания: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Всё запитано</t>
+          <t xml:space="preserve">Военное здание рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4353,44 +4361,48 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле не меньше 2 своих зданий, и все они запитаны</t>
-        </is>
-      </c>
-      <c r="F21" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть здание врага</t>
+        </is>
+      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">energy_swap|assembly</t>
-        </is>
-      </c>
-      <c r="K21" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">assembly|movement</t>
+        </is>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M21" s="2"/>
+        <v>0.0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей свои военные здания на 2 разных гексах, соседних с гексами, где есть здание врага</t>
+        </is>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
+      <c r="Q21" s="2">
+        <v>1</v>
+      </c>
       <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+      <c r="S21" s="2">
+        <v>2</v>
+      </c>
       <c r="T21" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле не меньше 2 своих зданий, и все они запитаны — награда на выбор: Питание или Снабжение и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Снабжение или Манёвр. Дополнительно — имей свои военные здания на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4414,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Военное здание ×2</t>
+          <t xml:space="preserve">Боеприпасы ×3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4417,7 +4429,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих военных здания</t>
+          <t xml:space="preserve">Имей не меньше 3 боеприпасов</t>
         </is>
       </c>
       <c r="F22" s="2"/>
@@ -4429,36 +4441,30 @@
           <t xml:space="preserve">build_military|movement</t>
         </is>
       </c>
-      <c r="K22" s="2"/>
+      <c r="K22" s="2">
+        <v>2</v>
+      </c>
       <c r="L22" s="2">
         <v>0.0</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей на поле 3 своих военных здания</t>
-        </is>
-      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
-      <c r="Q22" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
-      <c r="S22" s="2">
-        <v>2</v>
-      </c>
+      <c r="S22" s="2"/>
       <c r="T22" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ</t>
+          <t xml:space="preserve">ЗАКРОМА. Получи 2 боеприпаса, если кто-либо атакует твой жетон</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих военных здания — награда на выбор: Построить военное здание или Манёвр. Дополнительно — имей на поле 3 своих военных здания: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей не меньше 3 боеприпасов — награда на выбор: Построить военное здание или Манёвр и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4476,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Военное здание рядом с врагом ×1</t>
+          <t xml:space="preserve">Выпусти ×2</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4480,12 +4486,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть здание врага</t>
+          <t xml:space="preserve">В ЭТОТ ХОД выпусти 2 боеприпаса</t>
         </is>
       </c>
       <c r="F23" s="2"/>
@@ -4497,36 +4503,30 @@
           <t xml:space="preserve">assembly|combat</t>
         </is>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="2">
+        <v>3</v>
+      </c>
       <c r="L23" s="2">
         <v>0.0</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей свои военные здания на 2 разных гексах, соседних с гексами, где есть здание врага</t>
-        </is>
-      </c>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
-      <c r="Q23" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="2">
-        <v>2</v>
-      </c>
+      <c r="S23" s="2"/>
       <c r="T23" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+          <t xml:space="preserve">ЩИТ: пехота или авиация</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Снабжение или Бой. Дополнительно — имей свои военные здания на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД выпусти 2 боеприпаса — награда на выбор: Снабжение или Бой и три спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боеприпасы ×3</t>
+          <t xml:space="preserve">Рода войск ×3</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4553,10 +4553,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 3 боеприпасов</t>
-        </is>
-      </c>
-      <c r="F24" s="2"/>
+          <t xml:space="preserve">Имей на поле свои войска 3 разных родов</t>
+        </is>
+      </c>
+      <c r="F24" s="2">
+        <v>2</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -4569,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="L24" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4579,16 +4581,16 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЗАКРОМА. Получи 2 боеприпаса, если кто-либо атакует твой жетон</t>
+          <t xml:space="preserve">СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 3 боеприпасов — награда на выбор: Построить военное здание или Бой и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле свои войска 3 разных родов — награда на выбор: Построить военное здание или Бой и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4602,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выпусти ×2</t>
+          <t xml:space="preserve">Боеприпасы и войска</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4610,15 +4612,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД выпусти 2 боеприпаса</t>
-        </is>
-      </c>
-      <c r="F25" s="2"/>
+          <t xml:space="preserve">Имей не меньше 2 боеприпасов и на поле 3 своих войска</t>
+        </is>
+      </c>
+      <c r="F25" s="2">
+        <v>2</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -4628,10 +4632,10 @@
         </is>
       </c>
       <c r="K25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -4641,16 +4645,16 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: пехота или авиация</t>
+          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД выпусти 2 боеприпаса — награда на выбор: Снабжение или Манёвр и три спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей не меньше 2 боеприпасов и на поле 3 своих войска — награда на выбор: Снабжение или Манёвр и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4666,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рода войск ×3</t>
+          <t xml:space="preserve">Военное здание рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4677,12 +4681,10 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои войска 3 разных родов</t>
-        </is>
-      </c>
-      <c r="F26" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть добытчик врага</t>
+        </is>
+      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -4691,30 +4693,36 @@
           <t xml:space="preserve">build_military|movement</t>
         </is>
       </c>
-      <c r="K26" s="2">
-        <v>2</v>
-      </c>
+      <c r="K26" s="2"/>
       <c r="L26" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M26" s="2"/>
+        <v>0.0</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей свои военные здания на 2 разных гексах, соседних с гексами, где есть добытчик врага</t>
+        </is>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
+      <c r="Q26" s="2">
+        <v>1</v>
+      </c>
       <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
+      <c r="S26" s="2">
+        <v>3</v>
+      </c>
       <c r="T26" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СНАРЯЖЕНИЕ ОДНИМ ЗДАНИЕМ</t>
+          <t xml:space="preserve">ЗАКРОМА. Получи 2 боеприпаса, если кто-либо атакует твой жетон</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои войска 3 разных родов — награда на выбор: Построить военное здание или Манёвр и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть добытчик врага — награда на выбор: Построить военное здание или Манёвр. Дополнительно — имей свои военные здания на 2 разных гексах, соседних с гексами, где есть добытчик врага: 1 карта арсенала и три спец-действия.</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4734,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боеприпасы и войска</t>
+          <t xml:space="preserve">Боеприпасы ×2</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4741,12 +4749,10 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 боеприпасов и на поле 3 своих войска</t>
-        </is>
-      </c>
-      <c r="F27" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей не меньше 2 боеприпасов</t>
+        </is>
+      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -4759,7 +4765,7 @@
         <v>2</v>
       </c>
       <c r="L27" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4769,16 +4775,16 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">РАЗВЁРТЫВАНИЕ: поставь 1 войско из запаса</t>
+          <t xml:space="preserve">ЩИТ: пехота или авиация</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 боеприпасов и на поле 3 своих войска — награда на выбор: Снабжение или Бой и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей не меньше 2 боеприпасов — награда на выбор: Снабжение или Бой и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4796,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Военное здание рядом с врагом ×1</t>
+          <t xml:space="preserve">Рода войск ×2</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4805,10 +4811,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть добытчик врага</t>
-        </is>
-      </c>
-      <c r="F28" s="2"/>
+          <t xml:space="preserve">Имей на поле свои войска 2 разных родов</t>
+        </is>
+      </c>
+      <c r="F28" s="2">
+        <v>2</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -4819,34 +4827,26 @@
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей свои военные здания на 2 разных гексах, соседних с гексами, где есть добытчик врага</t>
-        </is>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
-      <c r="Q28" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="2">
-        <v>3</v>
-      </c>
+      <c r="S28" s="2"/>
       <c r="T28" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЗАКРОМА. Получи 2 боеприпаса, если кто-либо атакует твой жетон</t>
+          <t xml:space="preserve">+1 СПЕЦ-ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей своё военное здание на гексе, соседнем с гексом, где есть добытчик врага — награда на выбор: Построить военное здание или Бой. Дополнительно — имей свои военные здания на 2 разных гексах, соседних с гексами, где есть добытчик врага: 1 карта арсенала и три спец-действия.</t>
+          <t xml:space="preserve">Имей на поле свои войска 2 разных родов — награда на выбор: Построить военное здание или Бой и 2 монеты. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Боеприпасы ×2</t>
+          <t xml:space="preserve">Техника ×2</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4873,42 +4873,50 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 боеприпасов</t>
+          <t xml:space="preserve">Имей на поле 2 своих жетона техники</t>
         </is>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assembly|movement</t>
-        </is>
-      </c>
-      <c r="K29" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">movement|market</t>
+        </is>
+      </c>
+      <c r="K29" s="2"/>
       <c r="L29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M29" s="2"/>
+        <v>2.0</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей на поле 3 своих жетона техники</t>
+        </is>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
+      <c r="Q29" s="2">
+        <v>1</v>
+      </c>
       <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
+      <c r="S29" s="2">
+        <v>2</v>
+      </c>
       <c r="T29" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЩИТ: пехота или авиация</t>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 боеприпасов — награда на выбор: Снабжение или Манёвр и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле 2 своих жетона техники — награда на выбор: Манёвр или Рынок и 1 трофей. Дополнительно — имей на поле 3 своих жетона техники: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4928,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рода войск ×2</t>
+          <t xml:space="preserve">Авиация рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4935,42 +4943,50 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои войска 2 разных родов</t>
-        </is>
-      </c>
-      <c r="F30" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей свой жетон авиации на гексе, соседнем с гексом, где есть войско врага</t>
+        </is>
+      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">build_military|movement</t>
+          <t xml:space="preserve">combat|market</t>
         </is>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2">
         <v>2.0</v>
       </c>
-      <c r="M30" s="2"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей свои жетоны авиации на 2 разных гексах, соседних с гексами, где есть войско врага</t>
+        </is>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
+      <c r="Q30" s="2">
+        <v>1</v>
+      </c>
       <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
+      <c r="S30" s="2">
+        <v>2</v>
+      </c>
       <c r="T30" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 СПЕЦ-ДЕЙСТВИЕ</t>
+          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле свои войска 2 разных родов — награда на выбор: Построить военное здание или Манёвр и 2 монеты. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей свой жетон авиации на гексе, соседнем с гексом, где есть войско врага — награда на выбор: Бой или Рынок и 1 трофей. Дополнительно — имей свои жетоны авиации на 2 разных гексах, соседних с гексами, где есть войско врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -4982,7 +4998,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Техника ×2</t>
+          <t xml:space="preserve">Бой и Наука</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4992,12 +5008,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих жетона техники</t>
+          <t xml:space="preserve">В ЭТОТ ХОД сыграй «Бой» и «Наука»</t>
         </is>
       </c>
       <c r="F31" s="2"/>
@@ -5011,36 +5027,30 @@
           <t xml:space="preserve">movement|science</t>
         </is>
       </c>
-      <c r="K31" s="2"/>
+      <c r="K31" s="2">
+        <v>3</v>
+      </c>
       <c r="L31" s="2">
         <v>2.0</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей на поле 3 своих жетона техники</t>
-        </is>
-      </c>
+      <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
-      <c r="Q31" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
-      <c r="S31" s="2">
-        <v>2</v>
-      </c>
+      <c r="S31" s="2"/>
       <c r="T31" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих жетона техники — награда на выбор: Манёвр или Наука и 1 трофей. Дополнительно — имей на поле 3 своих жетона техники: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД сыграй «Бой» и «Наука» — награда на выбор: Манёвр или Наука и 1 трофей и три спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5062,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Авиация рядом с врагом ×1</t>
+          <t xml:space="preserve">Уничтожь жетон ×1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -5062,12 +5072,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой жетон авиации на гексе, соседнем с гексом, где есть войско врага</t>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон врага</t>
         </is>
       </c>
       <c r="F32" s="2"/>
@@ -5087,7 +5097,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей свои жетоны авиации на 2 разных гексах, соседних с гексами, где есть войско врага</t>
+          <t xml:space="preserve">уничтожь 2 жетона врага</t>
         </is>
       </c>
       <c r="N32" s="2"/>
@@ -5098,19 +5108,19 @@
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" s="2">
         <v>4.0</v>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой жетон авиации на гексе, соседнем с гексом, где есть войско врага — награда на выбор: Бой или Наука и 1 трофей. Дополнительно — имей свои жетоны авиации на 2 разных гексах, соседних с гексами, где есть войско врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон врага — награда на выбор: Бой или Наука и 1 трофей. Дополнительно — уничтожь 2 жетона врага: 1 карта арсенала и три спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5132,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бой и Наука</t>
+          <t xml:space="preserve">Авиация ×2</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -5132,12 +5142,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД сыграй «Бой» и «Наука»</t>
+          <t xml:space="preserve">Имей на поле 2 своих жетона авиации</t>
         </is>
       </c>
       <c r="F33" s="2"/>
@@ -5151,30 +5161,36 @@
           <t xml:space="preserve">movement|market</t>
         </is>
       </c>
-      <c r="K33" s="2">
-        <v>3</v>
-      </c>
+      <c r="K33" s="2"/>
       <c r="L33" s="2">
         <v>2.0</v>
       </c>
-      <c r="M33" s="2"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей на поле 3 своих жетона авиации</t>
+        </is>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
+      <c r="Q33" s="2">
+        <v>1</v>
+      </c>
       <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
+      <c r="S33" s="2">
+        <v>2</v>
+      </c>
       <c r="T33" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД сыграй «Бой» и «Наука» — награда на выбор: Манёвр или Рынок и 1 трофей и три спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле 2 своих жетона авиации — награда на выбор: Манёвр или Рынок и 1 трофей. Дополнительно — имей на поле 3 своих жетона авиации: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5202,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уничтожь жетон ×1</t>
+          <t xml:space="preserve">Войско рядом с врагом ×2</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5196,12 +5212,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон врага</t>
+          <t xml:space="preserve">Имей свои войска на 2 разных гексах, соседних с гексами, где есть добытчик врага</t>
         </is>
       </c>
       <c r="F34" s="2"/>
@@ -5221,7 +5237,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">уничтожь 2 жетона врага</t>
+          <t xml:space="preserve">имей свои войска на 3 разных гексах, соседних с гексами, где есть добытчик врага</t>
         </is>
       </c>
       <c r="N34" s="2"/>
@@ -5232,19 +5248,19 @@
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" s="2">
         <v>4.0</v>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
+          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь жетон врага — награда на выбор: Бой или Рынок и 1 трофей. Дополнительно — уничтожь 2 жетона врага: 1 карта арсенала и три спец-действия.</t>
+          <t xml:space="preserve">Имей свои войска на 2 разных гексах, соседних с гексами, где есть добытчик врага — награда на выбор: Бой или Рынок и 1 трофей. Дополнительно — имей свои войска на 3 разных гексах, соседних с гексами, где есть добытчик врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5272,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Авиация ×2</t>
+          <t xml:space="preserve">Уничтожь здание ×1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5266,12 +5282,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих жетона авиации</t>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь здание врага</t>
         </is>
       </c>
       <c r="F35" s="2"/>
@@ -5291,7 +5307,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей на поле 3 своих жетона авиации</t>
+          <t xml:space="preserve">уничтожь 2 здания врага</t>
         </is>
       </c>
       <c r="N35" s="2"/>
@@ -5302,19 +5318,19 @@
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" s="2">
         <v>4.0</v>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих жетона авиации — награда на выбор: Манёвр или Наука и 1 трофей. Дополнительно — имей на поле 3 своих жетона авиации: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД уничтожь здание врага — награда на выбор: Манёвр или Наука и 1 трофей. Дополнительно — уничтожь 2 здания врага: 1 карта арсенала и три спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5342,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Войско рядом с врагом ×2</t>
+          <t xml:space="preserve">Пехота ×2</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -5341,7 +5357,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свои войска на 2 разных гексах, соседних с гексами, где есть добытчик врага</t>
+          <t xml:space="preserve">Имей на поле 2 своих жетона пехоты</t>
         </is>
       </c>
       <c r="F36" s="2"/>
@@ -5361,7 +5377,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей свои войска на 3 разных гексах, соседних с гексами, где есть добытчик врага</t>
+          <t xml:space="preserve">имей на поле 3 своих жетона пехоты</t>
         </is>
       </c>
       <c r="N36" s="2"/>
@@ -5379,12 +5395,12 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свои войска на 2 разных гексах, соседних с гексами, где есть добытчик врага — награда на выбор: Бой или Наука и 1 трофей. Дополнительно — имей свои войска на 3 разных гексах, соседних с гексами, где есть добытчик врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей на поле 2 своих жетона пехоты — награда на выбор: Бой или Наука и 1 трофей. Дополнительно — имей на поле 3 своих жетона пехоты: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5412,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уничтожь здание ×1</t>
+          <t xml:space="preserve">Техника рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -5406,12 +5422,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь здание врага</t>
+          <t xml:space="preserve">Имей свой жетон техники на гексе, соседнем с гексом, где есть здание врага</t>
         </is>
       </c>
       <c r="F37" s="2"/>
@@ -5431,7 +5447,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">уничтожь 2 здания врага</t>
+          <t xml:space="preserve">имей свои жетоны техники на 2 разных гексах, соседних с гексами, где есть здание врага</t>
         </is>
       </c>
       <c r="N37" s="2"/>
@@ -5442,19 +5458,19 @@
       </c>
       <c r="R37" s="2"/>
       <c r="S37" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T37" s="2">
         <v>4.0</v>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
+          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД уничтожь здание врага — награда на выбор: Манёвр или Рынок и 1 трофей. Дополнительно — уничтожь 2 здания врага: 1 карта арсенала и три спец-действия.</t>
+          <t xml:space="preserve">Имей свой жетон техники на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Манёвр или Рынок и 1 трофей. Дополнительно — имей свои жетоны техники на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5482,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пехота ×2</t>
+          <t xml:space="preserve">Войско ×4</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -5481,7 +5497,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих жетона пехоты</t>
+          <t xml:space="preserve">Имей на поле 4 своих войска</t>
         </is>
       </c>
       <c r="F38" s="2"/>
@@ -5501,7 +5517,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей на поле 3 своих жетона пехоты</t>
+          <t xml:space="preserve">имей на поле 5 своих войск</t>
         </is>
       </c>
       <c r="N38" s="2"/>
@@ -5519,12 +5535,12 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
+          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 2 своих жетона пехоты — награда на выбор: Бой или Рынок и 1 трофей. Дополнительно — имей на поле 3 своих жетона пехоты: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей на поле 4 своих войска — награда на выбор: Бой или Рынок и 1 трофей. Дополнительно — имей на поле 5 своих войск: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5552,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Техника рядом с врагом ×1</t>
+          <t xml:space="preserve">Монеты ×8</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -5551,50 +5567,42 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой жетон техники на гексе, соседнем с гексом, где есть здание врага</t>
+          <t xml:space="preserve">Имей не меньше 8 монет</t>
         </is>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2">
-        <v>1</v>
-      </c>
+      <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">movement|science</t>
-        </is>
-      </c>
-      <c r="K39" s="2"/>
+          <t xml:space="preserve">market|build_miner</t>
+        </is>
+      </c>
+      <c r="K39" s="2">
+        <v>2</v>
+      </c>
       <c r="L39" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей свои жетоны техники на 2 разных гексах, соседних с гексами, где есть здание врага</t>
-        </is>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
-      <c r="Q39" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="2">
-        <v>2</v>
-      </c>
+      <c r="S39" s="2"/>
       <c r="T39" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНОЕ ДВИЖЕНИЕ</t>
+          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой жетон техники на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Манёвр или Наука и 1 трофей. Дополнительно — имей свои жетоны техники на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей не меньше 8 монет — награда на выбор: Рынок или Построить добытчик и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5614,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Войско ×4</t>
+          <t xml:space="preserve">Арсенал ×2</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5621,27 +5629,25 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 4 своих войска</t>
+          <t xml:space="preserve">Имей 2 установленные карты арсенала</t>
         </is>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2">
-        <v>1</v>
-      </c>
+      <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">combat|science</t>
+          <t xml:space="preserve">science|build_miner</t>
         </is>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей на поле 5 своих войск</t>
+          <t xml:space="preserve">имей 3 установленные карты арсенала</t>
         </is>
       </c>
       <c r="N40" s="2"/>
@@ -5659,12 +5665,12 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t xml:space="preserve">СВОБОДНАЯ НАУКА</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на поле 4 своих войска — награда на выбор: Бой или Наука и 1 трофей. Дополнительно — имей на поле 5 своих войск: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей 2 установленные карты арсенала — награда на выбор: Наука или Построить добытчик. Дополнительно — имей 3 установленные карты арсенала: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5682,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Монеты ×8</t>
+          <t xml:space="preserve">Второе спец-действие</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5686,12 +5692,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние</t>
+          <t xml:space="preserve">происшествие</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 8 монет</t>
+          <t xml:space="preserve">В ЭТОТ ХОД выполни это задание вторым спец-действием хода</t>
         </is>
       </c>
       <c r="F41" s="2"/>
@@ -5704,7 +5710,7 @@
         </is>
       </c>
       <c r="K41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2">
         <v>0.0</v>
@@ -5721,12 +5727,12 @@
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
+          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 8 монет — награда на выбор: Рынок или Добыча и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">В ЭТОТ ХОД выполни это задание вторым спец-действием хода — награда на выбор: Рынок или Добыча и три спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5744,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Арсенал ×2</t>
+          <t xml:space="preserve">Наука на 2 треках</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -5753,7 +5759,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей 2 установленные карты арсенала</t>
+          <t xml:space="preserve">Имей кубики науки на 2 треках</t>
         </is>
       </c>
       <c r="F42" s="2"/>
@@ -5765,36 +5771,30 @@
           <t xml:space="preserve">science|mining</t>
         </is>
       </c>
-      <c r="K42" s="2"/>
+      <c r="K42" s="2">
+        <v>2</v>
+      </c>
       <c r="L42" s="2">
         <v>0.0</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">имей 3 установленные карты арсенала</t>
-        </is>
-      </c>
+      <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
-      <c r="Q42" s="2">
-        <v>1</v>
-      </c>
+      <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
-      <c r="S42" s="2">
-        <v>2</v>
-      </c>
+      <c r="S42" s="2"/>
       <c r="T42" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНАЯ НАУКА</t>
+          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей 2 установленные карты арсенала — награда на выбор: Наука или Добыча. Дополнительно — имей 3 установленные карты арсенала: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей кубики науки на 2 треках — награда на выбор: Наука или Добыча и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Второе спец-действие</t>
+          <t xml:space="preserve">Модули ×2</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5816,15 +5816,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">происшествие</t>
+          <t xml:space="preserve">состояние</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД выполни это задание вторым спец-действием хода</t>
-        </is>
-      </c>
-      <c r="F43" s="2"/>
+          <t xml:space="preserve">Имей на планшете войск 2 модуля</t>
+        </is>
+      </c>
+      <c r="F43" s="2">
+        <v>2</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -5834,10 +5836,10 @@
         </is>
       </c>
       <c r="K43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -5847,16 +5849,16 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
+          <t xml:space="preserve">СВОБОДНАЯ НАУКА</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В ЭТОТ ХОД выполни это задание вторым спец-действием хода — награда на выбор: Рынок или Построить добытчик и три спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на планшете войск 2 модуля — награда на выбор: Рынок или Построить добытчик и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5870,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наука на 2 треках</t>
+          <t xml:space="preserve">Келемий ×2</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5883,7 +5885,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей кубики науки на 2 треках</t>
+          <t xml:space="preserve">Имей не меньше 2 келемия</t>
         </is>
       </c>
       <c r="F44" s="2"/>
@@ -5913,12 +5915,12 @@
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
+          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей кубики науки на 2 треках — награда на выбор: Наука или Построить добытчик и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей не меньше 2 келемия — награда на выбор: Наука или Построить добытчик и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5932,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Модули ×2</t>
+          <t xml:space="preserve">Наука на 1 треке, ступень 3+</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -5945,12 +5947,10 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на планшете войск 2 модуля</t>
-        </is>
-      </c>
-      <c r="F45" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей кубики науки на 1 треке на ступени 3 или выше</t>
+        </is>
+      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -5963,7 +5963,7 @@
         <v>2</v>
       </c>
       <c r="L45" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -5973,16 +5973,16 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНАЯ НАУКА</t>
+          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на планшете войск 2 модуля — награда на выбор: Рынок или Добыча и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей кубики науки на 1 треке на ступени 3 или выше — награда на выбор: Рынок или Добыча и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Келемий ×2</t>
+          <t xml:space="preserve">Золотые модули ×1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 келемия</t>
+          <t xml:space="preserve">Имей на планшете войск 1 золотой модуль</t>
         </is>
       </c>
       <c r="F46" s="2"/>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="K46" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2">
         <v>0.0</v>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
+          <t xml:space="preserve">СВОБОДНАЯ НАУКА</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 келемия — награда на выбор: Наука или Добыча и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на планшете войск 1 золотой модуль — награда на выбор: Наука или Добыча и три спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наука на 1 треке, ступень 3+</t>
+          <t xml:space="preserve">Трофеи ×2</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -6071,10 +6071,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей кубики науки на 1 треке на ступени 3 или выше</t>
-        </is>
-      </c>
-      <c r="F47" s="2"/>
+          <t xml:space="preserve">Имей не меньше 2 трофеев</t>
+        </is>
+      </c>
+      <c r="F47" s="2">
+        <v>2</v>
+      </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -6087,7 +6089,7 @@
         <v>2</v>
       </c>
       <c r="L47" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6097,16 +6099,16 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
+          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей кубики науки на 1 треке на ступени 3 или выше — награда на выбор: Рынок или Построить добытчик и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей не меньше 2 трофеев — награда на выбор: Рынок или Построить добытчик и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6120,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Золотые модули ×1</t>
+          <t xml:space="preserve">Арсенал ×3</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6133,10 +6135,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на планшете войск 1 золотой модуль</t>
-        </is>
-      </c>
-      <c r="F48" s="2"/>
+          <t xml:space="preserve">Имей 3 установленные карты арсенала</t>
+        </is>
+      </c>
+      <c r="F48" s="2">
+        <v>2</v>
+      </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -6146,10 +6150,10 @@
         </is>
       </c>
       <c r="K48" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -6159,16 +6163,16 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНАЯ НАУКА</t>
+          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей на планшете войск 1 золотой модуль — награда на выбор: Наука или Построить добытчик и три спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей 3 установленные карты арсенала — награда на выбор: Наука или Построить добытчик и 2 монеты и два спец-действия. Усиления у карты нет.</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6184,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофеи ×2</t>
+          <t xml:space="preserve">Пехота рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6195,44 +6199,50 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 трофеев</t>
-        </is>
-      </c>
-      <c r="F49" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей свой жетон пехоты на гексе, соседнем с гексом, где есть ЦУ врага</t>
+        </is>
+      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="H49" s="2">
+        <v>1</v>
+      </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">market|mining</t>
-        </is>
-      </c>
-      <c r="K49" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">movement|market</t>
+        </is>
+      </c>
+      <c r="K49" s="2"/>
       <c r="L49" s="2">
         <v>2.0</v>
       </c>
-      <c r="M49" s="2"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей свои жетоны пехоты на 2 разных гексах, соседних с гексами, где есть ЦУ врага</t>
+        </is>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
+      <c r="Q49" s="2">
+        <v>1</v>
+      </c>
       <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
+      <c r="S49" s="2">
+        <v>2</v>
+      </c>
       <c r="T49" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ОБМЕН В НАУКЕ (не трек) ИЛИ 1 ОБМЕН НА РЫНКЕ (не карта)</t>
+          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей не меньше 2 трофеев — награда на выбор: Рынок или Добыча и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей свой жетон пехоты на гексе, соседнем с гексом, где есть ЦУ врага — награда на выбор: Манёвр или Рынок и 1 трофей. Дополнительно — имей свои жетоны пехоты на 2 разных гексах, соседних с гексами, где есть ЦУ врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6254,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Арсенал ×3</t>
+          <t xml:space="preserve">Войско ×4</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -6259,44 +6269,50 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей 3 установленные карты арсенала</t>
-        </is>
-      </c>
-      <c r="F50" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">Имей на поле 4 своих войска на разных гексах</t>
+        </is>
+      </c>
+      <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
+      <c r="H50" s="2">
+        <v>1</v>
+      </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">science|mining</t>
-        </is>
-      </c>
-      <c r="K50" s="2">
-        <v>2</v>
-      </c>
+          <t xml:space="preserve">combat|market</t>
+        </is>
+      </c>
+      <c r="K50" s="2"/>
       <c r="L50" s="2">
         <v>2.0</v>
       </c>
-      <c r="M50" s="2"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">имей на поле 5 своих войск на разных гексах</t>
+        </is>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
+      <c r="Q50" s="2">
+        <v>1</v>
+      </c>
       <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
+      <c r="S50" s="2">
+        <v>3</v>
+      </c>
       <c r="T50" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СВОБОДНЫЙ РЫНОК</t>
+          <t xml:space="preserve">+1 К СКОРОСТИ ОДНОГО РОДА ДО КОНЦА ХОДА</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей 3 установленные карты арсенала — награда на выбор: Наука или Добыча и 2 монеты и два спец-действия. Усиления у карты нет.</t>
+          <t xml:space="preserve">Имей на поле 4 своих войска на разных гексах — награда на выбор: Бой или Рынок и 1 трофей. Дополнительно — имей на поле 5 своих войск на разных гексах: 1 карта арсенала и три спец-действия.</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6324,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пехота рядом с врагом ×1</t>
+          <t xml:space="preserve">Энергостанция рядом с врагом ×1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -6323,27 +6339,25 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой жетон пехоты на гексе, соседнем с гексом, где есть ЦУ врага</t>
+          <t xml:space="preserve">Имей свою энергостанцию на гексе, соседнем с гексом, где есть здание врага</t>
         </is>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="2">
-        <v>1</v>
-      </c>
+      <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">movement|science</t>
+          <t xml:space="preserve">energy_swap|build_military</t>
         </is>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">имей свои жетоны пехоты на 2 разных гексах, соседних с гексами, где есть ЦУ врага</t>
+          <t xml:space="preserve">имей свои энергостанции на 2 разных гексах, соседних с гексами, где есть здание врага</t>
         </is>
       </c>
       <c r="N51" s="2"/>
@@ -6361,12 +6375,12 @@
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОТХОД: в чужой Бой уведи один свой жетон из атакуемого гекса на один гекс</t>
+          <t xml:space="preserve">Перемести любые жетоны модулей на планшете войск</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имей свой жетон пехоты на гексе, соседнем с гексом, где есть ЦУ врага — награда на выбор: Манёвр или Наука и 1 трофей. Дополнительно — имей свои жетоны пехоты на 2 разных гексах, соседних с гексами, где есть ЦУ врага: 1 карта арсенала и два спец-действия.</t>
+          <t xml:space="preserve">Имей свою энергостанцию на гексе, соседнем с гексом, где есть здание врага — награда на выбор: Питание или Построить военное здание. Дополнительно — имей свои энергостанции на 2 разных гексах, соседних с гексами, где есть здание врага: 1 карта арсенала и два спец-действия.</t>
         </is>
       </c>
     </row>
